--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N105_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N105_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.12187894729942</v>
+        <v>9.607305328936157</v>
       </c>
       <c r="D2" t="n">
-        <v>36.52744193304484</v>
+        <v>5.935709314119787</v>
       </c>
       <c r="E2" t="n">
-        <v>17.71397634197705</v>
+        <v>2.878521155571271</v>
       </c>
       <c r="F2" t="n">
-        <v>7.957961637488222</v>
+        <v>1.293168766091836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.64140718935327</v>
+        <v>5.466728668269906</v>
       </c>
       <c r="D3" t="n">
-        <v>29.88417922752065</v>
+        <v>4.856179124472106</v>
       </c>
       <c r="E3" t="n">
-        <v>17.71397634197705</v>
+        <v>2.878521155571271</v>
       </c>
       <c r="F3" t="n">
-        <v>7.957961637488222</v>
+        <v>1.293168766091836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.96632653959475</v>
+        <v>2.594528062684148</v>
       </c>
       <c r="D4" t="n">
-        <v>49.07658516364344</v>
+        <v>7.974945089092059</v>
       </c>
       <c r="E4" t="n">
-        <v>17.71397634197705</v>
+        <v>2.878521155571271</v>
       </c>
       <c r="F4" t="n">
-        <v>7.957961637488222</v>
+        <v>1.293168766091836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
